--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484855_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484855_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0391</v>
+        <v>1.8531</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9739</v>
+        <v>1.9996</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.1465</v>
       </c>
       <c r="G2" t="n">
         <v>1.9614</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1305</v>
+        <v>-0.0555</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0081</v>
+        <v>0.0337</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1224</v>
+        <v>-0.0893</v>
       </c>
       <c r="V2" t="n">
         <v>0.1359</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0482</v>
+        <v>0.1985</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1498</v>
+        <v>-0.0524</v>
       </c>
       <c r="F6" t="n">
-        <v>0.198</v>
+        <v>0.2509</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0021</v>
@@ -922,13 +922,13 @@
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.308</v>
+        <v>-0.1577</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2939</v>
+        <v>-0.1965</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0141</v>
+        <v>0.0388</v>
       </c>
       <c r="V6" t="n">
         <v>1.547</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2106</v>
+        <v>-1.0543</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2397</v>
+        <v>-0.0835</v>
       </c>
       <c r="F7" t="n">
         <v>-0.9708</v>
@@ -1000,10 +1000,10 @@
         <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7671</v>
+        <v>-0.6109</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4904</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1205</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.823</v>
+        <v>-1.7352</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7202</v>
+        <v>-1.8177</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1028</v>
+        <v>0.0824</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3927</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0529</v>
+        <v>0.0348</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3556</v>
+        <v>0.2582</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4085</v>
+        <v>-0.2234</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1301</v>
+        <v>-2.4165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9808</v>
+        <v>0.7473</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1109</v>
+        <v>-3.1638</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7492</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4373</v>
+        <v>-0.7238</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1735</v>
+        <v>-0.407</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2639</v>
+        <v>-0.3168</v>
       </c>
       <c r="V9" t="n">
         <v>1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5917</v>
+        <v>-2.5556</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6571</v>
+        <v>-2.4622</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0654</v>
+        <v>-0.0934</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7488</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3562</v>
+        <v>-0.3201</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5879</v>
+        <v>-0.393</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2317</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4867</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2124</v>
+        <v>-2.7374</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5949</v>
+        <v>-0.1464</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6175</v>
+        <v>-2.591</v>
       </c>
       <c r="G11" t="n">
         <v>1.3626</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4237</v>
+        <v>-0.9488</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9406</v>
+        <v>-0.4921</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4831</v>
+        <v>-0.4567</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3208</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0967</v>
+        <v>-3.8101</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4435</v>
+        <v>-1.2851</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6532</v>
+        <v>-2.525</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1331</v>
+        <v>-2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0989</v>
+        <v>-0.2379</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2321</v>
+        <v>-1.7621</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9082</v>
+        <v>0.6283</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4653</v>
+        <v>1.1786</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5571</v>
+        <v>-0.5503</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0413</v>
+        <v>-2.6283</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3664</v>
+        <v>-1.4165</v>
       </c>
       <c r="O12" t="n">
-        <v>0.325</v>
+        <v>-1.2118</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2644</v>
+        <v>-2.6418</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.774</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0517</v>
+        <v>-1.4738</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1205</v>
+        <v>-0.6298</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0687</v>
+        <v>-0.8441</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7509</v>
+        <v>2.3055</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3018</v>
+        <v>2.4904</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0527</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5677</v>
+        <v>-4.2651</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.831</v>
+        <v>-2.6384</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7366</v>
+        <v>-1.6267</v>
       </c>
       <c r="G13" t="n">
-        <v>-2</v>
+        <v>-0.1331</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2379</v>
+        <v>2.0989</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7621</v>
+        <v>-2.2321</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6283</v>
+        <v>0.9082</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1786</v>
+        <v>3.4653</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5503</v>
+        <v>-2.5571</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6283</v>
+        <v>-1.0413</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4165</v>
+        <v>-1.3664</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2118</v>
+        <v>0.325</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.6418</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q13" t="n">
         <v>-3.774</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2314</v>
+        <v>-0.1167</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1758</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0557</v>
+        <v>-0.0423</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3055</v>
+        <v>-1.7509</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4904</v>
+        <v>0.3018</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1849</v>
+        <v>-2.0527</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.1628</v>
+        <v>-5.1918</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.6552</v>
+        <v>-2.499</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5076</v>
+        <v>-2.6927</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6125</v>
@@ -1546,13 +1546,13 @@
         <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5502</v>
+        <v>-0.5792</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5879</v>
+        <v>-0.4317</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0377</v>
+        <v>-0.1475</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3018</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.873699999999999</v>
+        <v>-8.573</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.3422</v>
+        <v>-5.1474</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5314</v>
+        <v>-3.4256</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6773</v>
@@ -1624,13 +1624,13 @@
         <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0863</v>
+        <v>-0.7856</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.823</v>
+        <v>-0.6282</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2633</v>
+        <v>-0.1575</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8265</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.7627</v>
+        <v>-27.4687</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.8602</v>
+        <v>-10.5665</v>
       </c>
       <c r="F16" t="n">
         <v>-16.9022</v>
@@ -1702,13 +1702,13 @@
         <v>9.435</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.030899999999999</v>
+        <v>-5.737299999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.7451</v>
+        <v>-3.4512</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.286</v>
+        <v>-2.2864</v>
       </c>
       <c r="V16" t="n">
         <v>0.9433</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.0019</v>
+        <v>5.3932</v>
       </c>
       <c r="E17" t="n">
-        <v>7.4571</v>
+        <v>3.6826</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4553</v>
+        <v>1.7106</v>
       </c>
       <c r="G17" t="n">
-        <v>4.9132</v>
+        <v>3.2557</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2199</v>
+        <v>4.5437</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6933</v>
+        <v>-1.2881</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1443</v>
+        <v>4.6539</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1873</v>
+        <v>5.7474</v>
       </c>
       <c r="L17" t="n">
-        <v>3.957</v>
+        <v>-1.0935</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2311</v>
+        <v>-1.3982</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9674</v>
+        <v>-1.2036</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7363</v>
+        <v>-0.1946</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>3.5853</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8433</v>
+        <v>0.7601</v>
       </c>
       <c r="T17" t="n">
-        <v>3.0867</v>
+        <v>0.3121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.566</v>
+        <v>-0.3208</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8678</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7123</v>
+        <v>4.8235</v>
       </c>
       <c r="E18" t="n">
-        <v>3.094</v>
+        <v>5.411</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6183</v>
+        <v>-0.5875</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9994</v>
+        <v>4.9132</v>
       </c>
       <c r="H18" t="n">
-        <v>2.03</v>
+        <v>0.2199</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0306</v>
+        <v>4.6933</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2451</v>
+        <v>6.1443</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4449</v>
+        <v>2.1873</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1998</v>
+        <v>3.957</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2457</v>
+        <v>-1.2311</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4149</v>
+        <v>-1.9674</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1692</v>
+        <v>0.7363</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R18" t="n">
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7694</v>
+        <v>1.6649</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5472</v>
+        <v>1.0406</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2222</v>
+        <v>0.6243</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.566</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.6402</v>
+        <v>4.3504</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9031</v>
+        <v>2.9966</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7371</v>
+        <v>1.3537</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2557</v>
+        <v>1.9994</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5437</v>
+        <v>2.03</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2881</v>
+        <v>-0.0306</v>
       </c>
       <c r="J19" t="n">
-        <v>4.6539</v>
+        <v>2.2451</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7474</v>
+        <v>3.4449</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0935</v>
+        <v>-1.1998</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3982</v>
+        <v>-0.2457</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2036</v>
+        <v>-1.4149</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1946</v>
+        <v>1.1692</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5853</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.007</v>
+        <v>1.4074</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4674</v>
+        <v>0.4498</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4744</v>
+        <v>0.9577</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.9164</v>
+        <v>3.6241</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1776</v>
+        <v>1.8853</v>
       </c>
       <c r="F20" t="n">
         <v>1.7389</v>
@@ -2014,10 +2014,10 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9805</v>
+        <v>0.6882</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4296</v>
+        <v>0.1373</v>
       </c>
       <c r="U20" t="n">
         <v>0.5508999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2915</v>
+        <v>3.5225</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6819</v>
+        <v>2.0716</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6096</v>
+        <v>1.4509</v>
       </c>
       <c r="G21" t="n">
         <v>2.4343</v>
@@ -2092,13 +2092,13 @@
         <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4233</v>
+        <v>0.6543</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2816</v>
+        <v>0.1081</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7049</v>
+        <v>0.5461</v>
       </c>
       <c r="V21" t="n">
         <v>0.6226</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.0812</v>
+        <v>3.1161</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3707</v>
+        <v>2.2733</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7105</v>
+        <v>0.8428</v>
       </c>
       <c r="G22" t="n">
         <v>0.4615</v>
@@ -2170,13 +2170,13 @@
         <v>3.0192</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0911</v>
+        <v>0.1259</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3585</v>
+        <v>0.2611</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2674</v>
+        <v>-0.1352</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3018</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4498</v>
+        <v>2.5653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1308</v>
+        <v>0.3257</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3189</v>
+        <v>2.2396</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6857</v>
@@ -2248,13 +2248,13 @@
         <v>3.2079</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9276</v>
+        <v>1.0431</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3585</v>
+        <v>0.5534</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4897</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4269</v>
+        <v>1.896</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3289</v>
+        <v>0.7186</v>
       </c>
       <c r="F24" t="n">
-        <v>1.098</v>
+        <v>1.1774</v>
       </c>
       <c r="G24" t="n">
         <v>0.8079</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5132</v>
+        <v>-0.0441</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>-0.0094</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.114</v>
+        <v>-0.0347</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4815</v>
+        <v>-0.1568</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4561</v>
+        <v>0.5304</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9745</v>
+        <v>-0.6872</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3935</v>
+        <v>-1.2122</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.1899</v>
+        <v>-3.2642</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2037</v>
+        <v>2.052</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0497</v>
+        <v>1.6866</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.149</v>
+        <v>-0.3217</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0993</v>
+        <v>2.0083</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3438</v>
+        <v>-2.8989</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0408</v>
+        <v>-2.9425</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.303</v>
+        <v>0.0437</v>
       </c>
       <c r="P25" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0757</v>
+        <v>4.3401</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5155</v>
+        <v>-0.4542</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5937</v>
+        <v>-0.4953</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0412</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3208</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.4294</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.342</v>
+        <v>-1.0497</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4351</v>
+        <v>0.6203</v>
       </c>
       <c r="G26" t="n">
         <v>-1.2392</v>
@@ -2482,13 +2482,13 @@
         <v>0.3774</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3468</v>
+        <v>0.1306</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4703</v>
+        <v>-0.178</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1235</v>
+        <v>0.3086</v>
       </c>
       <c r="V26" t="n">
         <v>0.3018</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.3692</v>
+        <v>-0.9423</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4439</v>
+        <v>-1.9432</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9253</v>
+        <v>1.001</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.2122</v>
+        <v>-3.3935</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.2642</v>
+        <v>-3.1899</v>
       </c>
       <c r="I27" t="n">
-        <v>2.052</v>
+        <v>-0.2037</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6866</v>
+        <v>-2.0497</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.3217</v>
+        <v>-2.149</v>
       </c>
       <c r="L27" t="n">
-        <v>2.0083</v>
+        <v>0.0993</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.8989</v>
+        <v>-1.3438</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.9425</v>
+        <v>-1.0408</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0437</v>
+        <v>-0.303</v>
       </c>
       <c r="P27" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.3401</v>
+        <v>2.0757</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6666</v>
+        <v>0.0548</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4697</v>
+        <v>0.1065</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1969</v>
+        <v>-0.0517</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W27" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.1696</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="28">
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>27.7627</v>
+        <v>27.7626</v>
       </c>
       <c r="E28" t="n">
-        <v>16.9021</v>
+        <v>16.9022</v>
       </c>
       <c r="F28" t="n">
-        <v>10.8603</v>
+        <v>10.8605</v>
       </c>
       <c r="G28" t="n">
-        <v>7.579</v>
+        <v>7.579000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>-3.5688</v>
@@ -2638,13 +2638,13 @@
         <v>24.531</v>
       </c>
       <c r="S28" t="n">
-        <v>6.031099999999999</v>
+        <v>6.031</v>
       </c>
       <c r="T28" t="n">
-        <v>2.286</v>
+        <v>2.2862</v>
       </c>
       <c r="U28" t="n">
-        <v>3.7451</v>
+        <v>3.7449</v>
       </c>
       <c r="V28" t="n">
         <v>-0.9434</v>
